--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1010_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1010_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,15 +441,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Sea Ice</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Natalie Wood</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Grandfather Clocks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -463,12 +473,18 @@
         <v>0.03630303591489792</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.06252215802669525</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.3343283534049988</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.2472030371427536</v>
       </c>
     </row>
@@ -480,12 +496,18 @@
         <v>-0.01883880980312824</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.05069379508495331</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.3278546929359436</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.2245103716850281</v>
       </c>
     </row>
@@ -497,12 +519,18 @@
         <v>0.01789974793791771</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.6809456348419189</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.1382090449333191</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.4230227470397949</v>
       </c>
     </row>
@@ -517,9 +545,15 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.5160688161849976</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.3987464904785156</v>
       </c>
     </row>
@@ -531,12 +565,18 @@
         <v>0.1488000899553299</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.3488845229148865</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.4332852959632874</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.2592801451683044</v>
       </c>
     </row>
@@ -548,12 +588,18 @@
         <v>0.596409797668457</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.1633833646774292</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.5927017331123352</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.4831080138683319</v>
       </c>
     </row>
@@ -565,12 +611,18 @@
         <v>0.7139962911605835</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.1923616528511047</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.3937101662158966</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.2889754474163055</v>
       </c>
     </row>
@@ -582,12 +634,18 @@
         <v>0.3360586166381836</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.159587949514389</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>0.7157636880874634</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.2485349774360657</v>
       </c>
     </row>
@@ -602,9 +660,15 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.4931144118309021</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.5171961784362793</v>
       </c>
     </row>
@@ -616,12 +680,18 @@
         <v>0.1810076832771301</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.4514236450195312</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.5041732788085938</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,9 +706,15 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.5034823417663574</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -650,12 +726,18 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.4351220726966858</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.6355090141296387</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -667,12 +749,18 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.5164003372192383</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.4138763546943665</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -684,12 +772,18 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.4304590821266174</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.3549717366695404</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.1742561459541321</v>
       </c>
     </row>
@@ -704,9 +798,15 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.3945574760437012</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -721,9 +821,15 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.3107383847236633</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.310729593038559</v>
       </c>
     </row>
@@ -735,12 +841,18 @@
         <v>0.1556445956230164</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>-0.02452240139245987</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.5687506198883057</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.288000226020813</v>
       </c>
     </row>
@@ -752,12 +864,16 @@
         <v>0.47689089179039</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.3086964786052704</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0.4188846051692963</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -772,9 +888,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.60362708568573</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -792,6 +912,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0.227717712521553</v>
       </c>
     </row>
@@ -809,6 +933,10 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -824,6 +952,10 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -834,9 +966,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.487310528755188</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -845,13 +981,15 @@
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>0.2731783986091614</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,13 +998,15 @@
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>0.5104847550392151</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -875,13 +1015,15 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>0.1153960376977921</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -890,13 +1032,15 @@
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>0.4420779943466187</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0.2856126129627228</v>
       </c>
     </row>
@@ -905,13 +1049,15 @@
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>0.4833787679672241</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.3805549144744873</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0.3794572651386261</v>
       </c>
     </row>
@@ -920,13 +1066,15 @@
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
         <v>0.3411415815353394</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.1679867506027222</v>
       </c>
     </row>
@@ -935,11 +1083,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -948,11 +1098,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0.2352202534675598</v>
       </c>
     </row>
@@ -961,11 +1113,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.7191024422645569</v>
       </c>
     </row>
@@ -974,11 +1128,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.6672807335853577</v>
       </c>
     </row>
@@ -987,11 +1143,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.6536228060722351</v>
       </c>
     </row>
@@ -1000,11 +1158,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.5944033861160278</v>
       </c>
     </row>
@@ -1013,11 +1173,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1026,11 +1188,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1039,11 +1203,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1052,11 +1218,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0.1420696377754211</v>
       </c>
     </row>
@@ -1065,11 +1233,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.2495025843381882</v>
       </c>
     </row>
@@ -1078,11 +1248,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.1669322848320007</v>
       </c>
     </row>
@@ -1091,154 +1263,182 @@
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
